--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataNew19072026\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\Zlaata04082026\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A487A85F-B99F-4D71-8E71-22E4C1D513C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E71E61-786F-4D46-9DDC-000A5B79BEA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6921" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6955" uniqueCount="775">
   <si>
     <t>S.No</t>
   </si>
@@ -2317,9 +2317,6 @@
     <t>Verify login popup appears when guest user clicks Apply button in coupon section on cart page</t>
   </si>
   <si>
-    <t>Verify validation message appears when guest user clicks Gift Card Amount section on cart page</t>
-  </si>
-  <si>
     <t>Verify validation message appears when guest user clicks Threads on cart page</t>
   </si>
   <si>
@@ -2339,6 +2336,21 @@
   </si>
   <si>
     <t>Verify login popup appears when guest user clicks Profile icon in the Landing Page</t>
+  </si>
+  <si>
+    <t>Gift card</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GC_01</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to add a Gift Card to the cart</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GC_01</t>
+  </si>
+  <si>
+    <t>Verify that the Login Popup is displayed when the user clicks the Notify Me when Available button on the Product Details Page.</t>
   </si>
 </sst>
 </file>
@@ -2805,7 +2817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3047,6 +3059,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3082,9 +3098,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3888,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z223"/>
+  <dimension ref="A1:Z225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -4639,18 +4652,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="97" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
@@ -5037,18 +5050,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="98" t="s">
+      <c r="A37" s="100" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
@@ -5723,18 +5736,18 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="95" t="s">
+      <c r="A59" s="97" t="s">
         <v>234</v>
       </c>
-      <c r="B59" s="96"/>
-      <c r="C59" s="96"/>
-      <c r="D59" s="96"/>
-      <c r="E59" s="96"/>
-      <c r="F59" s="96"/>
-      <c r="G59" s="96"/>
-      <c r="H59" s="96"/>
-      <c r="I59" s="96"/>
-      <c r="J59" s="97"/>
+      <c r="B59" s="98"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="98"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="98"/>
+      <c r="G59" s="98"/>
+      <c r="H59" s="98"/>
+      <c r="I59" s="98"/>
+      <c r="J59" s="99"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
@@ -6057,18 +6070,18 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="98" t="s">
+      <c r="A70" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="B70" s="99"/>
-      <c r="C70" s="99"/>
-      <c r="D70" s="99"/>
-      <c r="E70" s="99"/>
-      <c r="F70" s="99"/>
-      <c r="G70" s="99"/>
-      <c r="H70" s="99"/>
-      <c r="I70" s="99"/>
-      <c r="J70" s="100"/>
+      <c r="B70" s="101"/>
+      <c r="C70" s="101"/>
+      <c r="D70" s="101"/>
+      <c r="E70" s="101"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="101"/>
+      <c r="J70" s="102"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25">
@@ -6487,18 +6500,18 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="98" t="s">
+      <c r="A84" s="100" t="s">
         <v>334</v>
       </c>
-      <c r="B84" s="99"/>
-      <c r="C84" s="99"/>
-      <c r="D84" s="99"/>
-      <c r="E84" s="99"/>
-      <c r="F84" s="99"/>
-      <c r="G84" s="99"/>
-      <c r="H84" s="99"/>
-      <c r="I84" s="99"/>
-      <c r="J84" s="100"/>
+      <c r="B84" s="101"/>
+      <c r="C84" s="101"/>
+      <c r="D84" s="101"/>
+      <c r="E84" s="101"/>
+      <c r="F84" s="101"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="101"/>
+      <c r="I84" s="101"/>
+      <c r="J84" s="102"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
@@ -7365,18 +7378,18 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="101" t="s">
+      <c r="A112" s="103" t="s">
         <v>364</v>
       </c>
-      <c r="B112" s="101"/>
-      <c r="C112" s="101"/>
-      <c r="D112" s="101"/>
-      <c r="E112" s="101"/>
-      <c r="F112" s="101"/>
-      <c r="G112" s="101"/>
-      <c r="H112" s="101"/>
-      <c r="I112" s="101"/>
-      <c r="J112" s="101"/>
+      <c r="B112" s="103"/>
+      <c r="C112" s="103"/>
+      <c r="D112" s="103"/>
+      <c r="E112" s="103"/>
+      <c r="F112" s="103"/>
+      <c r="G112" s="103"/>
+      <c r="H112" s="103"/>
+      <c r="I112" s="103"/>
+      <c r="J112" s="103"/>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
@@ -7699,18 +7712,18 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A123" s="102" t="s">
+      <c r="A123" s="104" t="s">
         <v>366</v>
       </c>
-      <c r="B123" s="102"/>
-      <c r="C123" s="102"/>
-      <c r="D123" s="102"/>
-      <c r="E123" s="102"/>
-      <c r="F123" s="102"/>
-      <c r="G123" s="102"/>
-      <c r="H123" s="102"/>
-      <c r="I123" s="102"/>
-      <c r="J123" s="102"/>
+      <c r="B123" s="104"/>
+      <c r="C123" s="104"/>
+      <c r="D123" s="104"/>
+      <c r="E123" s="104"/>
+      <c r="F123" s="104"/>
+      <c r="G123" s="104"/>
+      <c r="H123" s="104"/>
+      <c r="I123" s="104"/>
+      <c r="J123" s="104"/>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="25">
@@ -7745,18 +7758,18 @@
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="102" t="s">
+      <c r="A125" s="104" t="s">
         <v>371</v>
       </c>
-      <c r="B125" s="102"/>
-      <c r="C125" s="102"/>
-      <c r="D125" s="102"/>
-      <c r="E125" s="102"/>
-      <c r="F125" s="102"/>
-      <c r="G125" s="102"/>
-      <c r="H125" s="102"/>
-      <c r="I125" s="102"/>
-      <c r="J125" s="102"/>
+      <c r="B125" s="104"/>
+      <c r="C125" s="104"/>
+      <c r="D125" s="104"/>
+      <c r="E125" s="104"/>
+      <c r="F125" s="104"/>
+      <c r="G125" s="104"/>
+      <c r="H125" s="104"/>
+      <c r="I125" s="104"/>
+      <c r="J125" s="104"/>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="25">
@@ -7791,18 +7804,18 @@
       </c>
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="102" t="s">
+      <c r="A127" s="104" t="s">
         <v>384</v>
       </c>
-      <c r="B127" s="102"/>
-      <c r="C127" s="102"/>
-      <c r="D127" s="102"/>
-      <c r="E127" s="102"/>
-      <c r="F127" s="102"/>
-      <c r="G127" s="102"/>
-      <c r="H127" s="102"/>
-      <c r="I127" s="102"/>
-      <c r="J127" s="102"/>
+      <c r="B127" s="104"/>
+      <c r="C127" s="104"/>
+      <c r="D127" s="104"/>
+      <c r="E127" s="104"/>
+      <c r="F127" s="104"/>
+      <c r="G127" s="104"/>
+      <c r="H127" s="104"/>
+      <c r="I127" s="104"/>
+      <c r="J127" s="104"/>
     </row>
     <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
@@ -8587,18 +8600,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="102" t="s">
+      <c r="A145" s="104" t="s">
         <v>396</v>
       </c>
-      <c r="B145" s="102"/>
-      <c r="C145" s="102"/>
-      <c r="D145" s="103"/>
-      <c r="E145" s="103"/>
-      <c r="F145" s="103"/>
-      <c r="G145" s="103"/>
-      <c r="H145" s="103"/>
-      <c r="I145" s="103"/>
-      <c r="J145" s="103"/>
+      <c r="B145" s="104"/>
+      <c r="C145" s="104"/>
+      <c r="D145" s="105"/>
+      <c r="E145" s="105"/>
+      <c r="F145" s="105"/>
+      <c r="G145" s="105"/>
+      <c r="H145" s="105"/>
+      <c r="I145" s="105"/>
+      <c r="J145" s="105"/>
     </row>
     <row r="146" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="59">
@@ -9061,18 +9074,18 @@
       <c r="X155" s="58"/>
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="104" t="s">
+      <c r="A156" s="106" t="s">
         <v>425</v>
       </c>
-      <c r="B156" s="105"/>
-      <c r="C156" s="105"/>
-      <c r="D156" s="105"/>
-      <c r="E156" s="105"/>
-      <c r="F156" s="105"/>
-      <c r="G156" s="105"/>
-      <c r="H156" s="105"/>
-      <c r="I156" s="105"/>
-      <c r="J156" s="106"/>
+      <c r="B156" s="107"/>
+      <c r="C156" s="107"/>
+      <c r="D156" s="107"/>
+      <c r="E156" s="107"/>
+      <c r="F156" s="107"/>
+      <c r="G156" s="107"/>
+      <c r="H156" s="107"/>
+      <c r="I156" s="107"/>
+      <c r="J156" s="108"/>
     </row>
     <row r="157" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
@@ -9659,18 +9672,18 @@
       <c r="X169" s="58"/>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A170" s="102" t="s">
+      <c r="A170" s="104" t="s">
         <v>497</v>
       </c>
-      <c r="B170" s="102"/>
-      <c r="C170" s="102"/>
-      <c r="D170" s="102"/>
-      <c r="E170" s="102"/>
-      <c r="F170" s="102"/>
-      <c r="G170" s="102"/>
-      <c r="H170" s="102"/>
-      <c r="I170" s="102"/>
-      <c r="J170" s="102"/>
+      <c r="B170" s="104"/>
+      <c r="C170" s="104"/>
+      <c r="D170" s="104"/>
+      <c r="E170" s="104"/>
+      <c r="F170" s="104"/>
+      <c r="G170" s="104"/>
+      <c r="H170" s="104"/>
+      <c r="I170" s="104"/>
+      <c r="J170" s="104"/>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="25">
@@ -9737,18 +9750,18 @@
       </c>
     </row>
     <row r="173" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="102" t="s">
+      <c r="A173" s="104" t="s">
         <v>523</v>
       </c>
-      <c r="B173" s="102"/>
-      <c r="C173" s="102"/>
-      <c r="D173" s="102"/>
-      <c r="E173" s="102"/>
-      <c r="F173" s="102"/>
-      <c r="G173" s="102"/>
-      <c r="H173" s="102"/>
-      <c r="I173" s="102"/>
-      <c r="J173" s="102"/>
+      <c r="B173" s="104"/>
+      <c r="C173" s="104"/>
+      <c r="D173" s="104"/>
+      <c r="E173" s="104"/>
+      <c r="F173" s="104"/>
+      <c r="G173" s="104"/>
+      <c r="H173" s="104"/>
+      <c r="I173" s="104"/>
+      <c r="J173" s="104"/>
     </row>
     <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="65">
@@ -10615,18 +10628,18 @@
       <c r="Z191" s="58"/>
     </row>
     <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="102" t="s">
+      <c r="A192" s="104" t="s">
         <v>602</v>
       </c>
-      <c r="B192" s="102"/>
-      <c r="C192" s="102"/>
-      <c r="D192" s="102"/>
-      <c r="E192" s="102"/>
-      <c r="F192" s="102"/>
-      <c r="G192" s="102"/>
-      <c r="H192" s="102"/>
-      <c r="I192" s="102"/>
-      <c r="J192" s="102"/>
+      <c r="B192" s="104"/>
+      <c r="C192" s="104"/>
+      <c r="D192" s="104"/>
+      <c r="E192" s="104"/>
+      <c r="F192" s="104"/>
+      <c r="G192" s="104"/>
+      <c r="H192" s="104"/>
+      <c r="I192" s="104"/>
+      <c r="J192" s="104"/>
     </row>
     <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="73">
@@ -10853,18 +10866,18 @@
       </c>
     </row>
     <row r="200" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="102" t="s">
+      <c r="A200" s="104" t="s">
         <v>602</v>
       </c>
-      <c r="B200" s="102"/>
-      <c r="C200" s="102"/>
-      <c r="D200" s="102"/>
-      <c r="E200" s="102"/>
-      <c r="F200" s="102"/>
-      <c r="G200" s="102"/>
-      <c r="H200" s="102"/>
-      <c r="I200" s="102"/>
-      <c r="J200" s="102"/>
+      <c r="B200" s="104"/>
+      <c r="C200" s="104"/>
+      <c r="D200" s="104"/>
+      <c r="E200" s="104"/>
+      <c r="F200" s="104"/>
+      <c r="G200" s="104"/>
+      <c r="H200" s="104"/>
+      <c r="I200" s="104"/>
+      <c r="J200" s="104"/>
     </row>
     <row r="201" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="73">
@@ -10899,18 +10912,18 @@
       </c>
     </row>
     <row r="202" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="107" t="s">
+      <c r="A202" s="96" t="s">
         <v>665</v>
       </c>
-      <c r="B202" s="107"/>
-      <c r="C202" s="107"/>
-      <c r="D202" s="107"/>
-      <c r="E202" s="107"/>
-      <c r="F202" s="107"/>
-      <c r="G202" s="107"/>
-      <c r="H202" s="107"/>
-      <c r="I202" s="107"/>
-      <c r="J202" s="107"/>
+      <c r="B202" s="96"/>
+      <c r="C202" s="96"/>
+      <c r="D202" s="96"/>
+      <c r="E202" s="96"/>
+      <c r="F202" s="96"/>
+      <c r="G202" s="96"/>
+      <c r="H202" s="96"/>
+      <c r="I202" s="96"/>
+      <c r="J202" s="96"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="88">
@@ -11137,18 +11150,18 @@
       </c>
     </row>
     <row r="210" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="107" t="s">
+      <c r="A210" s="96" t="s">
         <v>731</v>
       </c>
-      <c r="B210" s="107"/>
-      <c r="C210" s="107"/>
-      <c r="D210" s="107"/>
-      <c r="E210" s="107"/>
-      <c r="F210" s="107"/>
-      <c r="G210" s="107"/>
-      <c r="H210" s="107"/>
-      <c r="I210" s="107"/>
-      <c r="J210" s="107"/>
+      <c r="B210" s="96"/>
+      <c r="C210" s="96"/>
+      <c r="D210" s="96"/>
+      <c r="E210" s="96"/>
+      <c r="F210" s="96"/>
+      <c r="G210" s="96"/>
+      <c r="H210" s="96"/>
+      <c r="I210" s="96"/>
+      <c r="J210" s="96"/>
     </row>
     <row r="211" spans="1:10" s="92" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="91">
@@ -11158,16 +11171,16 @@
         <v>10</v>
       </c>
       <c r="C211" s="89" t="s">
+        <v>768</v>
+      </c>
+      <c r="D211" s="94" t="s">
         <v>769</v>
-      </c>
-      <c r="D211" s="94" t="s">
-        <v>770</v>
       </c>
       <c r="E211" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="89" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G211" s="51" t="s">
         <v>11</v>
@@ -11417,7 +11430,7 @@
         <v>752</v>
       </c>
       <c r="D219" s="45" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E219" s="51" t="s">
         <v>14</v>
@@ -11449,7 +11462,7 @@
         <v>753</v>
       </c>
       <c r="D220" s="45" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E220" s="51" t="s">
         <v>14</v>
@@ -11481,7 +11494,7 @@
         <v>754</v>
       </c>
       <c r="D221" s="45" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E221" s="51" t="s">
         <v>14</v>
@@ -11513,7 +11526,7 @@
         <v>755</v>
       </c>
       <c r="D222" s="45" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E222" s="51" t="s">
         <v>14</v>
@@ -11534,7 +11547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="91">
         <v>13</v>
       </c>
@@ -11545,7 +11558,7 @@
         <v>756</v>
       </c>
       <c r="D223" s="45" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="E223" s="51" t="s">
         <v>14</v>
@@ -11566,13 +11579,62 @@
         <v>13</v>
       </c>
     </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="96" t="s">
+        <v>770</v>
+      </c>
+      <c r="B224" s="96"/>
+      <c r="C224" s="96"/>
+      <c r="D224" s="96"/>
+      <c r="E224" s="96"/>
+      <c r="F224" s="96"/>
+      <c r="G224" s="96"/>
+      <c r="H224" s="96"/>
+      <c r="I224" s="96"/>
+      <c r="J224" s="96"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="28">
+        <v>1</v>
+      </c>
+      <c r="B225" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C225" s="87" t="s">
+        <v>771</v>
+      </c>
+      <c r="D225" s="95" t="s">
+        <v>772</v>
+      </c>
+      <c r="E225" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F225" s="87" t="s">
+        <v>773</v>
+      </c>
+      <c r="G225" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="86" t="s">
+        <v>636</v>
+      </c>
+      <c r="I225" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J225" s="86" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A210:J210"/>
-    <mergeCell ref="A202:J202"/>
-    <mergeCell ref="A127:J127"/>
+  <mergeCells count="18">
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A224:J224"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A84:J84"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A200:J200"/>
     <mergeCell ref="A192:J192"/>
@@ -11580,11 +11642,9 @@
     <mergeCell ref="A170:J170"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A210:J210"/>
+    <mergeCell ref="A202:J202"/>
+    <mergeCell ref="A127:J127"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -11682,7 +11742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X216"/>
+  <dimension ref="A1:X217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -26459,7 +26519,7 @@
     </row>
     <row r="204" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A204" s="89" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B204" s="48" t="s">
         <v>22</v>
@@ -27416,6 +27476,80 @@
         <v>22</v>
       </c>
       <c r="X216" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A217" s="87" t="s">
+        <v>773</v>
+      </c>
+      <c r="B217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V217" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W217" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X217" s="48" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\Zlaata04082026\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\Zlaata03102026\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E71E61-786F-4D46-9DDC-000A5B79BEA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA695561-B1F0-4334-AE16-FAF602C38152}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6955" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7188" uniqueCount="797">
   <si>
     <t>S.No</t>
   </si>
@@ -1297,9 +1297,6 @@
     <t>TC_UI_Zlaata_ADDP_10</t>
   </si>
   <si>
-    <t>Verify Continue Order button functionality on Delivery Address page</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_ADDP_10</t>
   </si>
   <si>
@@ -1465,9 +1462,6 @@
     <t>Priya</t>
   </si>
   <si>
-    <t>priya@gmail.com</t>
-  </si>
-  <si>
     <t>TN Nagar</t>
   </si>
   <si>
@@ -1492,9 +1486,6 @@
     <t>Suba</t>
   </si>
   <si>
-    <t>sub@gmail.com</t>
-  </si>
-  <si>
     <t>uuuii</t>
   </si>
   <si>
@@ -2351,6 +2342,81 @@
   </si>
   <si>
     <t>Verify that the Login Popup is displayed when the user clicks the Notify Me when Available button on the Product Details Page.</t>
+  </si>
+  <si>
+    <t>Guest Login</t>
+  </si>
+  <si>
+    <t>Verify that the Guest Login button is available in the Login popup when clicking Place Order on the Checkout page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_02</t>
+  </si>
+  <si>
+    <t>Verify that the phone number field is not auto-populated when the user accesses the Address page through Guest Login</t>
+  </si>
+  <si>
+    <t>Verify that clicking the Save Address button without entering mandatory details on the Guest Address page displays validation messages</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_04</t>
+  </si>
+  <si>
+    <t>Verify that the Place Order button remains disabled on the Guest Address page when the mandatory address details are not entered</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_05</t>
+  </si>
+  <si>
+    <t>Verify that the user can enter valid address details on the Address page through Guest Login and the Estimated Delivery section is displayed</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_05</t>
+  </si>
+  <si>
+    <t>Verify that the user can edit the already entered address through Guest Login</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_GL_06</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_GL_06</t>
+  </si>
+  <si>
+    <t>roseberry12390987@gmail.com</t>
+  </si>
+  <si>
+    <t>Verify that the phone number on the Address page matches the phone number in Account Settings</t>
+  </si>
+  <si>
+    <t>Footer Logo Re-direction</t>
+  </si>
+  <si>
+    <t>Verify that clicking the Zlaata logo in footer on the Zlaata India website redirects the user to the Zlaata India Home page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FL_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FL_01</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2590,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2812,12 +2878,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3060,8 +3135,35 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3081,23 +3183,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3901,13 +3988,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z225"/>
+  <dimension ref="A1:Z235"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="123.28515625" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
@@ -3958,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -4652,18 +4739,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="108" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="99"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="109"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="110"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
@@ -4676,7 +4763,7 @@
         <v>61</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>14</v>
@@ -4708,7 +4795,7 @@
         <v>156</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>14</v>
@@ -5050,18 +5137,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="100" t="s">
+      <c r="A37" s="111" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="102"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
+      <c r="H37" s="112"/>
+      <c r="I37" s="112"/>
+      <c r="J37" s="113"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
@@ -5074,7 +5161,7 @@
         <v>171</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>14</v>
@@ -5138,7 +5225,7 @@
         <v>177</v>
       </c>
       <c r="D40" s="48" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>14</v>
@@ -5202,7 +5289,7 @@
         <v>182</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>14</v>
@@ -5234,7 +5321,7 @@
         <v>184</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>14</v>
@@ -5487,10 +5574,10 @@
         <v>10</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D51" s="48" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>14</v>
@@ -5519,10 +5606,10 @@
         <v>10</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
@@ -5551,16 +5638,16 @@
         <v>10</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="47" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G53" s="48" t="s">
         <v>11</v>
@@ -5583,16 +5670,16 @@
         <v>10</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F54" s="47" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G54" s="48" t="s">
         <v>11</v>
@@ -5615,16 +5702,16 @@
         <v>10</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E55" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="47" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G55" s="48" t="s">
         <v>11</v>
@@ -5647,16 +5734,16 @@
         <v>10</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E56" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F56" s="47" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G56" s="48" t="s">
         <v>11</v>
@@ -5679,16 +5766,16 @@
         <v>10</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D57" s="48" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E57" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F57" s="47" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="G57" s="48" t="s">
         <v>11</v>
@@ -5711,16 +5798,16 @@
         <v>10</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E58" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F58" s="47" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="G58" s="48" t="s">
         <v>11</v>
@@ -5736,18 +5823,18 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="97" t="s">
+      <c r="A59" s="108" t="s">
         <v>234</v>
       </c>
-      <c r="B59" s="98"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="98"/>
-      <c r="E59" s="98"/>
-      <c r="F59" s="98"/>
-      <c r="G59" s="98"/>
-      <c r="H59" s="98"/>
-      <c r="I59" s="98"/>
-      <c r="J59" s="99"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
+      <c r="J59" s="110"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
@@ -5760,7 +5847,7 @@
         <v>218</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>14</v>
@@ -5792,7 +5879,7 @@
         <v>220</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>14</v>
@@ -5824,7 +5911,7 @@
         <v>221</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>14</v>
@@ -5856,7 +5943,7 @@
         <v>222</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>14</v>
@@ -5888,7 +5975,7 @@
         <v>223</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E64" s="48" t="s">
         <v>14</v>
@@ -6070,18 +6157,18 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="100" t="s">
+      <c r="A70" s="111" t="s">
         <v>236</v>
       </c>
-      <c r="B70" s="101"/>
-      <c r="C70" s="101"/>
-      <c r="D70" s="101"/>
-      <c r="E70" s="101"/>
-      <c r="F70" s="101"/>
-      <c r="G70" s="101"/>
-      <c r="H70" s="101"/>
-      <c r="I70" s="101"/>
-      <c r="J70" s="102"/>
+      <c r="B70" s="112"/>
+      <c r="C70" s="112"/>
+      <c r="D70" s="112"/>
+      <c r="E70" s="112"/>
+      <c r="F70" s="112"/>
+      <c r="G70" s="112"/>
+      <c r="H70" s="112"/>
+      <c r="I70" s="112"/>
+      <c r="J70" s="113"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25">
@@ -6443,16 +6530,16 @@
         <v>10</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D82" s="48" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E82" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F82" s="48" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="G82" s="48" t="s">
         <v>11</v>
@@ -6475,16 +6562,16 @@
         <v>10</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D83" s="48" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E83" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="48" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G83" s="48" t="s">
         <v>11</v>
@@ -6500,18 +6587,18 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="100" t="s">
+      <c r="A84" s="111" t="s">
         <v>334</v>
       </c>
-      <c r="B84" s="101"/>
-      <c r="C84" s="101"/>
-      <c r="D84" s="101"/>
-      <c r="E84" s="101"/>
-      <c r="F84" s="101"/>
-      <c r="G84" s="101"/>
-      <c r="H84" s="101"/>
-      <c r="I84" s="101"/>
-      <c r="J84" s="102"/>
+      <c r="B84" s="112"/>
+      <c r="C84" s="112"/>
+      <c r="D84" s="112"/>
+      <c r="E84" s="112"/>
+      <c r="F84" s="112"/>
+      <c r="G84" s="112"/>
+      <c r="H84" s="112"/>
+      <c r="I84" s="112"/>
+      <c r="J84" s="113"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
@@ -6524,7 +6611,7 @@
         <v>271</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E85" s="48" t="s">
         <v>14</v>
@@ -6556,7 +6643,7 @@
         <v>274</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>14</v>
@@ -6588,7 +6675,7 @@
         <v>276</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E87" s="48" t="s">
         <v>14</v>
@@ -6620,7 +6707,7 @@
         <v>278</v>
       </c>
       <c r="D88" s="48" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E88" s="48" t="s">
         <v>14</v>
@@ -6652,7 +6739,7 @@
         <v>280</v>
       </c>
       <c r="D89" s="48" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E89" s="48" t="s">
         <v>14</v>
@@ -6812,7 +6899,7 @@
         <v>294</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E94" s="48" t="s">
         <v>14</v>
@@ -6844,7 +6931,7 @@
         <v>296</v>
       </c>
       <c r="D95" s="48" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E95" s="48" t="s">
         <v>14</v>
@@ -6876,7 +6963,7 @@
         <v>298</v>
       </c>
       <c r="D96" s="48" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E96" s="48" t="s">
         <v>14</v>
@@ -7036,7 +7123,7 @@
         <v>312</v>
       </c>
       <c r="D101" s="48" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E101" s="48" t="s">
         <v>14</v>
@@ -7132,7 +7219,7 @@
         <v>320</v>
       </c>
       <c r="D104" s="48" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E104" s="48" t="s">
         <v>14</v>
@@ -7164,7 +7251,7 @@
         <v>322</v>
       </c>
       <c r="D105" s="48" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E105" s="48" t="s">
         <v>14</v>
@@ -7196,7 +7283,7 @@
         <v>324</v>
       </c>
       <c r="D106" s="48" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E106" s="48" t="s">
         <v>14</v>
@@ -7228,7 +7315,7 @@
         <v>326</v>
       </c>
       <c r="D107" s="48" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E107" s="48" t="s">
         <v>14</v>
@@ -7260,7 +7347,7 @@
         <v>328</v>
       </c>
       <c r="D108" s="48" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E108" s="48" t="s">
         <v>14</v>
@@ -7292,7 +7379,7 @@
         <v>330</v>
       </c>
       <c r="D109" s="48" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E109" s="48" t="s">
         <v>14</v>
@@ -7353,16 +7440,16 @@
         <v>10</v>
       </c>
       <c r="C111" s="48" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D111" s="48" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E111" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="48" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G111" s="48" t="s">
         <v>11</v>
@@ -7378,18 +7465,18 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="103" t="s">
+      <c r="A112" s="102" t="s">
         <v>364</v>
       </c>
-      <c r="B112" s="103"/>
-      <c r="C112" s="103"/>
-      <c r="D112" s="103"/>
-      <c r="E112" s="103"/>
-      <c r="F112" s="103"/>
-      <c r="G112" s="103"/>
-      <c r="H112" s="103"/>
-      <c r="I112" s="103"/>
-      <c r="J112" s="103"/>
+      <c r="B112" s="102"/>
+      <c r="C112" s="102"/>
+      <c r="D112" s="102"/>
+      <c r="E112" s="102"/>
+      <c r="F112" s="102"/>
+      <c r="G112" s="102"/>
+      <c r="H112" s="102"/>
+      <c r="I112" s="102"/>
+      <c r="J112" s="102"/>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
@@ -7687,16 +7774,16 @@
         <v>10</v>
       </c>
       <c r="C122" s="48" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D122" s="48" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E122" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G122" s="48" t="s">
         <v>11</v>
@@ -7712,18 +7799,18 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A123" s="104" t="s">
+      <c r="A123" s="103" t="s">
         <v>366</v>
       </c>
-      <c r="B123" s="104"/>
-      <c r="C123" s="104"/>
-      <c r="D123" s="104"/>
-      <c r="E123" s="104"/>
-      <c r="F123" s="104"/>
-      <c r="G123" s="104"/>
-      <c r="H123" s="104"/>
-      <c r="I123" s="104"/>
-      <c r="J123" s="104"/>
+      <c r="B123" s="103"/>
+      <c r="C123" s="103"/>
+      <c r="D123" s="103"/>
+      <c r="E123" s="103"/>
+      <c r="F123" s="103"/>
+      <c r="G123" s="103"/>
+      <c r="H123" s="103"/>
+      <c r="I123" s="103"/>
+      <c r="J123" s="103"/>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="25">
@@ -7758,18 +7845,18 @@
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="104" t="s">
+      <c r="A125" s="103" t="s">
         <v>371</v>
       </c>
-      <c r="B125" s="104"/>
-      <c r="C125" s="104"/>
-      <c r="D125" s="104"/>
-      <c r="E125" s="104"/>
-      <c r="F125" s="104"/>
-      <c r="G125" s="104"/>
-      <c r="H125" s="104"/>
-      <c r="I125" s="104"/>
-      <c r="J125" s="104"/>
+      <c r="B125" s="103"/>
+      <c r="C125" s="103"/>
+      <c r="D125" s="103"/>
+      <c r="E125" s="103"/>
+      <c r="F125" s="103"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="103"/>
+      <c r="I125" s="103"/>
+      <c r="J125" s="103"/>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="25">
@@ -7804,18 +7891,18 @@
       </c>
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="104" t="s">
+      <c r="A127" s="103" t="s">
         <v>384</v>
       </c>
-      <c r="B127" s="104"/>
-      <c r="C127" s="104"/>
-      <c r="D127" s="104"/>
-      <c r="E127" s="104"/>
-      <c r="F127" s="104"/>
-      <c r="G127" s="104"/>
-      <c r="H127" s="104"/>
-      <c r="I127" s="104"/>
-      <c r="J127" s="104"/>
+      <c r="B127" s="103"/>
+      <c r="C127" s="103"/>
+      <c r="D127" s="103"/>
+      <c r="E127" s="103"/>
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="103"/>
+      <c r="I127" s="103"/>
+      <c r="J127" s="103"/>
     </row>
     <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
@@ -7828,7 +7915,7 @@
         <v>385</v>
       </c>
       <c r="D128" s="51" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E128" s="51" t="s">
         <v>14</v>
@@ -7871,10 +7958,10 @@
         <v>10</v>
       </c>
       <c r="C129" s="48" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D129" s="63" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E129" s="48" t="s">
         <v>14</v>
@@ -7917,10 +8004,10 @@
         <v>10</v>
       </c>
       <c r="C130" s="48" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D130" s="64" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E130" s="48" t="s">
         <v>14</v>
@@ -7963,10 +8050,10 @@
         <v>10</v>
       </c>
       <c r="C131" s="48" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D131" s="64" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E131" s="48" t="s">
         <v>14</v>
@@ -8009,10 +8096,10 @@
         <v>10</v>
       </c>
       <c r="C132" s="48" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D132" s="64" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E132" s="48" t="s">
         <v>14</v>
@@ -8055,10 +8142,10 @@
         <v>10</v>
       </c>
       <c r="C133" s="48" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D133" s="64" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E133" s="48" t="s">
         <v>14</v>
@@ -8101,10 +8188,10 @@
         <v>10</v>
       </c>
       <c r="C134" s="48" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D134" s="64" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E134" s="48" t="s">
         <v>14</v>
@@ -8147,10 +8234,10 @@
         <v>10</v>
       </c>
       <c r="C135" s="48" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D135" s="63" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E135" s="48" t="s">
         <v>14</v>
@@ -8193,16 +8280,16 @@
         <v>10</v>
       </c>
       <c r="C136" s="48" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D136" s="63" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E136" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F136" s="48" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G136" s="48" t="s">
         <v>11</v>
@@ -8239,16 +8326,16 @@
         <v>10</v>
       </c>
       <c r="C137" s="48" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D137" s="63" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E137" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F137" s="48" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G137" s="48" t="s">
         <v>11</v>
@@ -8285,16 +8372,16 @@
         <v>10</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D138" s="63" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E138" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G138" s="48" t="s">
         <v>11</v>
@@ -8331,7 +8418,7 @@
         <v>10</v>
       </c>
       <c r="C139" s="48" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D139" s="64" t="s">
         <v>393</v>
@@ -8340,7 +8427,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="48" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G139" s="48" t="s">
         <v>11</v>
@@ -8377,16 +8464,16 @@
         <v>10</v>
       </c>
       <c r="C140" s="48" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D140" s="63" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E140" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F140" s="48" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G140" s="48" t="s">
         <v>11</v>
@@ -8423,16 +8510,16 @@
         <v>10</v>
       </c>
       <c r="C141" s="48" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D141" s="63" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E141" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F141" s="48" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G141" s="48" t="s">
         <v>11</v>
@@ -8469,16 +8556,16 @@
         <v>10</v>
       </c>
       <c r="C142" s="48" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D142" s="63" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E142" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="48" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G142" s="48" t="s">
         <v>11</v>
@@ -8515,16 +8602,16 @@
         <v>10</v>
       </c>
       <c r="C143" s="48" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D143" s="63" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E143" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F143" s="48" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G143" s="48" t="s">
         <v>11</v>
@@ -8561,16 +8648,16 @@
         <v>10</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D144" s="63" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E144" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G144" s="48" t="s">
         <v>11</v>
@@ -8600,18 +8687,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="104" t="s">
+      <c r="A145" s="103" t="s">
         <v>396</v>
       </c>
-      <c r="B145" s="104"/>
-      <c r="C145" s="104"/>
-      <c r="D145" s="105"/>
-      <c r="E145" s="105"/>
-      <c r="F145" s="105"/>
-      <c r="G145" s="105"/>
-      <c r="H145" s="105"/>
-      <c r="I145" s="105"/>
-      <c r="J145" s="105"/>
+      <c r="B145" s="103"/>
+      <c r="C145" s="103"/>
+      <c r="D145" s="104"/>
+      <c r="E145" s="104"/>
+      <c r="F145" s="104"/>
+      <c r="G145" s="104"/>
+      <c r="H145" s="104"/>
+      <c r="I145" s="104"/>
+      <c r="J145" s="104"/>
     </row>
     <row r="146" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="59">
@@ -8624,7 +8711,7 @@
         <v>397</v>
       </c>
       <c r="D146" s="60" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E146" s="27" t="s">
         <v>14</v>
@@ -8762,7 +8849,7 @@
         <v>406</v>
       </c>
       <c r="D149" s="27" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E149" s="27" t="s">
         <v>14</v>
@@ -8808,7 +8895,7 @@
         <v>408</v>
       </c>
       <c r="D150" s="27" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E150" s="27" t="s">
         <v>14</v>
@@ -9038,13 +9125,13 @@
         <v>422</v>
       </c>
       <c r="D155" s="27" t="s">
-        <v>423</v>
+        <v>792</v>
       </c>
       <c r="E155" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F155" s="48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G155" s="27" t="s">
         <v>11</v>
@@ -9074,18 +9161,18 @@
       <c r="X155" s="58"/>
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="106" t="s">
-        <v>425</v>
-      </c>
-      <c r="B156" s="107"/>
-      <c r="C156" s="107"/>
-      <c r="D156" s="107"/>
-      <c r="E156" s="107"/>
-      <c r="F156" s="107"/>
-      <c r="G156" s="107"/>
-      <c r="H156" s="107"/>
-      <c r="I156" s="107"/>
-      <c r="J156" s="108"/>
+      <c r="A156" s="105" t="s">
+        <v>424</v>
+      </c>
+      <c r="B156" s="106"/>
+      <c r="C156" s="106"/>
+      <c r="D156" s="106"/>
+      <c r="E156" s="106"/>
+      <c r="F156" s="106"/>
+      <c r="G156" s="106"/>
+      <c r="H156" s="106"/>
+      <c r="I156" s="106"/>
+      <c r="J156" s="107"/>
     </row>
     <row r="157" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
@@ -9095,22 +9182,22 @@
         <v>10</v>
       </c>
       <c r="C157" s="48" t="s">
+        <v>425</v>
+      </c>
+      <c r="D157" s="48" t="s">
         <v>426</v>
-      </c>
-      <c r="D157" s="48" t="s">
-        <v>427</v>
       </c>
       <c r="E157" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F157" s="48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G157" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H157" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I157" s="48" t="s">
         <v>12</v>
@@ -9141,22 +9228,22 @@
         <v>10</v>
       </c>
       <c r="C158" s="48" t="s">
+        <v>429</v>
+      </c>
+      <c r="D158" s="48" t="s">
         <v>430</v>
-      </c>
-      <c r="D158" s="48" t="s">
-        <v>431</v>
       </c>
       <c r="E158" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G158" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H158" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I158" s="48" t="s">
         <v>12</v>
@@ -9187,22 +9274,22 @@
         <v>10</v>
       </c>
       <c r="C159" s="48" t="s">
+        <v>432</v>
+      </c>
+      <c r="D159" s="48" t="s">
         <v>433</v>
-      </c>
-      <c r="D159" s="48" t="s">
-        <v>434</v>
       </c>
       <c r="E159" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F159" s="48" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G159" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H159" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I159" s="48" t="s">
         <v>12</v>
@@ -9233,22 +9320,22 @@
         <v>10</v>
       </c>
       <c r="C160" s="48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D160" s="48" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E160" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F160" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G160" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H160" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I160" s="48" t="s">
         <v>12</v>
@@ -9265,22 +9352,22 @@
         <v>10</v>
       </c>
       <c r="C161" s="48" t="s">
+        <v>437</v>
+      </c>
+      <c r="D161" s="48" t="s">
         <v>438</v>
-      </c>
-      <c r="D161" s="48" t="s">
-        <v>439</v>
       </c>
       <c r="E161" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F161" s="48" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G161" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H161" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I161" s="48" t="s">
         <v>12</v>
@@ -9311,22 +9398,22 @@
         <v>10</v>
       </c>
       <c r="C162" s="48" t="s">
+        <v>440</v>
+      </c>
+      <c r="D162" s="48" t="s">
         <v>441</v>
-      </c>
-      <c r="D162" s="48" t="s">
-        <v>442</v>
       </c>
       <c r="E162" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F162" s="48" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G162" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H162" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I162" s="48" t="s">
         <v>12</v>
@@ -9357,22 +9444,22 @@
         <v>10</v>
       </c>
       <c r="C163" s="48" t="s">
+        <v>443</v>
+      </c>
+      <c r="D163" s="48" t="s">
         <v>444</v>
-      </c>
-      <c r="D163" s="48" t="s">
-        <v>445</v>
       </c>
       <c r="E163" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F163" s="48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G163" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H163" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I163" s="48" t="s">
         <v>12</v>
@@ -9403,22 +9490,22 @@
         <v>10</v>
       </c>
       <c r="C164" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="D164" s="48" t="s">
         <v>447</v>
-      </c>
-      <c r="D164" s="48" t="s">
-        <v>448</v>
       </c>
       <c r="E164" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F164" s="48" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G164" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H164" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I164" s="48" t="s">
         <v>12</v>
@@ -9449,22 +9536,22 @@
         <v>10</v>
       </c>
       <c r="C165" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D165" s="48" t="s">
         <v>450</v>
-      </c>
-      <c r="D165" s="48" t="s">
-        <v>451</v>
       </c>
       <c r="E165" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F165" s="48" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G165" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H165" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I165" s="48" t="s">
         <v>12</v>
@@ -9495,22 +9582,22 @@
         <v>10</v>
       </c>
       <c r="C166" s="48" t="s">
+        <v>452</v>
+      </c>
+      <c r="D166" s="48" t="s">
         <v>453</v>
-      </c>
-      <c r="D166" s="48" t="s">
-        <v>454</v>
       </c>
       <c r="E166" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F166" s="48" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G166" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H166" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I166" s="48" t="s">
         <v>12</v>
@@ -9541,22 +9628,22 @@
         <v>10</v>
       </c>
       <c r="C167" s="48" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D167" s="48" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E167" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="48" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G167" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H167" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I167" s="48" t="s">
         <v>12</v>
@@ -9587,22 +9674,22 @@
         <v>10</v>
       </c>
       <c r="C168" s="48" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D168" s="48" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E168" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F168" s="48" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="G168" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H168" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I168" s="48" t="s">
         <v>12</v>
@@ -9633,22 +9720,22 @@
         <v>10</v>
       </c>
       <c r="C169" s="48" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D169" s="48" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E169" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F169" s="48" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G169" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H169" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I169" s="48" t="s">
         <v>12</v>
@@ -9672,18 +9759,18 @@
       <c r="X169" s="58"/>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A170" s="104" t="s">
-        <v>497</v>
-      </c>
-      <c r="B170" s="104"/>
-      <c r="C170" s="104"/>
-      <c r="D170" s="104"/>
-      <c r="E170" s="104"/>
-      <c r="F170" s="104"/>
-      <c r="G170" s="104"/>
-      <c r="H170" s="104"/>
-      <c r="I170" s="104"/>
-      <c r="J170" s="104"/>
+      <c r="A170" s="103" t="s">
+        <v>494</v>
+      </c>
+      <c r="B170" s="103"/>
+      <c r="C170" s="103"/>
+      <c r="D170" s="103"/>
+      <c r="E170" s="103"/>
+      <c r="F170" s="103"/>
+      <c r="G170" s="103"/>
+      <c r="H170" s="103"/>
+      <c r="I170" s="103"/>
+      <c r="J170" s="103"/>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="25">
@@ -9693,16 +9780,16 @@
         <v>10</v>
       </c>
       <c r="C171" s="48" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D171" s="24" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E171" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="48" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G171" s="48" t="s">
         <v>11</v>
@@ -9725,16 +9812,16 @@
         <v>10</v>
       </c>
       <c r="C172" s="48" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D172" s="24" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E172" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F172" s="48" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G172" s="48" t="s">
         <v>11</v>
@@ -9750,18 +9837,18 @@
       </c>
     </row>
     <row r="173" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="104" t="s">
-        <v>523</v>
-      </c>
-      <c r="B173" s="104"/>
-      <c r="C173" s="104"/>
-      <c r="D173" s="104"/>
-      <c r="E173" s="104"/>
-      <c r="F173" s="104"/>
-      <c r="G173" s="104"/>
-      <c r="H173" s="104"/>
-      <c r="I173" s="104"/>
-      <c r="J173" s="104"/>
+      <c r="A173" s="103" t="s">
+        <v>520</v>
+      </c>
+      <c r="B173" s="103"/>
+      <c r="C173" s="103"/>
+      <c r="D173" s="103"/>
+      <c r="E173" s="103"/>
+      <c r="F173" s="103"/>
+      <c r="G173" s="103"/>
+      <c r="H173" s="103"/>
+      <c r="I173" s="103"/>
+      <c r="J173" s="103"/>
     </row>
     <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="65">
@@ -9771,22 +9858,22 @@
         <v>10</v>
       </c>
       <c r="C174" s="67" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D174" s="66" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E174" s="66" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="67" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G174" s="66" t="s">
         <v>11</v>
       </c>
       <c r="H174" s="66" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I174" s="66" t="s">
         <v>12</v>
@@ -9819,22 +9906,22 @@
         <v>10</v>
       </c>
       <c r="C175" s="70" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D175" s="69" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E175" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="70" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G175" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H175" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I175" s="69" t="s">
         <v>12</v>
@@ -9867,22 +9954,22 @@
         <v>10</v>
       </c>
       <c r="C176" s="70" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D176" s="71" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E176" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F176" s="70" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G176" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H176" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I176" s="69" t="s">
         <v>12</v>
@@ -9915,22 +10002,22 @@
         <v>10</v>
       </c>
       <c r="C177" s="70" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D177" s="69" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E177" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F177" s="70" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G177" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H177" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I177" s="69" t="s">
         <v>12</v>
@@ -9963,22 +10050,22 @@
         <v>10</v>
       </c>
       <c r="C178" s="70" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D178" s="69" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E178" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="70" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G178" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H178" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I178" s="69" t="s">
         <v>12</v>
@@ -10011,22 +10098,22 @@
         <v>10</v>
       </c>
       <c r="C179" s="70" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D179" s="71" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E179" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F179" s="70" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G179" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H179" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I179" s="69" t="s">
         <v>12</v>
@@ -10059,22 +10146,22 @@
         <v>10</v>
       </c>
       <c r="C180" s="70" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D180" s="69" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E180" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F180" s="70" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G180" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H180" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I180" s="69" t="s">
         <v>12</v>
@@ -10107,22 +10194,22 @@
         <v>10</v>
       </c>
       <c r="C181" s="70" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D181" s="69" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E181" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F181" s="70" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G181" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H181" s="69" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I181" s="69" t="s">
         <v>12</v>
@@ -10155,22 +10242,22 @@
         <v>10</v>
       </c>
       <c r="C182" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D182" s="74" t="s">
         <v>545</v>
-      </c>
-      <c r="D182" s="74" t="s">
-        <v>548</v>
       </c>
       <c r="E182" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F182" s="75" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G182" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H182" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I182" s="74" t="s">
         <v>12</v>
@@ -10203,22 +10290,22 @@
         <v>10</v>
       </c>
       <c r="C183" s="75" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D183" s="74" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E183" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F183" s="75" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G183" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H183" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I183" s="74" t="s">
         <v>12</v>
@@ -10251,22 +10338,22 @@
         <v>10</v>
       </c>
       <c r="C184" s="75" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D184" s="74" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E184" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="75" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G184" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H184" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I184" s="74" t="s">
         <v>12</v>
@@ -10299,22 +10386,22 @@
         <v>10</v>
       </c>
       <c r="C185" s="75" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D185" s="74" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E185" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F185" s="75" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G185" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H185" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I185" s="74" t="s">
         <v>12</v>
@@ -10347,22 +10434,22 @@
         <v>10</v>
       </c>
       <c r="C186" s="75" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D186" s="74" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E186" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F186" s="75" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="G186" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H186" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I186" s="74" t="s">
         <v>12</v>
@@ -10395,22 +10482,22 @@
         <v>10</v>
       </c>
       <c r="C187" s="75" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D187" s="76" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E187" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F187" s="75" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="G187" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H187" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I187" s="74" t="s">
         <v>12</v>
@@ -10443,22 +10530,22 @@
         <v>10</v>
       </c>
       <c r="C188" s="75" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D188" s="76" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E188" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="75" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G188" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H188" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I188" s="74" t="s">
         <v>12</v>
@@ -10491,22 +10578,22 @@
         <v>10</v>
       </c>
       <c r="C189" s="75" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D189" s="76" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E189" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F189" s="75" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="G189" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H189" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I189" s="74" t="s">
         <v>12</v>
@@ -10539,22 +10626,22 @@
         <v>10</v>
       </c>
       <c r="C190" s="75" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D190" s="76" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E190" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F190" s="75" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G190" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H190" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I190" s="74" t="s">
         <v>12</v>
@@ -10587,22 +10674,22 @@
         <v>10</v>
       </c>
       <c r="C191" s="75" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D191" s="77" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E191" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F191" s="75" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="G191" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H191" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I191" s="74" t="s">
         <v>12</v>
@@ -10628,18 +10715,18 @@
       <c r="Z191" s="58"/>
     </row>
     <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="104" t="s">
-        <v>602</v>
-      </c>
-      <c r="B192" s="104"/>
-      <c r="C192" s="104"/>
-      <c r="D192" s="104"/>
-      <c r="E192" s="104"/>
-      <c r="F192" s="104"/>
-      <c r="G192" s="104"/>
-      <c r="H192" s="104"/>
-      <c r="I192" s="104"/>
-      <c r="J192" s="104"/>
+      <c r="A192" s="103" t="s">
+        <v>599</v>
+      </c>
+      <c r="B192" s="103"/>
+      <c r="C192" s="103"/>
+      <c r="D192" s="103"/>
+      <c r="E192" s="103"/>
+      <c r="F192" s="103"/>
+      <c r="G192" s="103"/>
+      <c r="H192" s="103"/>
+      <c r="I192" s="103"/>
+      <c r="J192" s="103"/>
     </row>
     <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="73">
@@ -10649,22 +10736,22 @@
         <v>10</v>
       </c>
       <c r="C193" s="75" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D193" s="77" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E193" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F193" s="75" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G193" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H193" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I193" s="74" t="s">
         <v>12</v>
@@ -10681,22 +10768,22 @@
         <v>10</v>
       </c>
       <c r="C194" s="75" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D194" s="77" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E194" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F194" s="75" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G194" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H194" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I194" s="74" t="s">
         <v>12</v>
@@ -10713,22 +10800,22 @@
         <v>10</v>
       </c>
       <c r="C195" s="75" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D195" s="81" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E195" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F195" s="75" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G195" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H195" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I195" s="74" t="s">
         <v>12</v>
@@ -10745,22 +10832,22 @@
         <v>10</v>
       </c>
       <c r="C196" s="79" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D196" s="64" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E196" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F196" s="75" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G196" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H196" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I196" s="74" t="s">
         <v>12</v>
@@ -10777,22 +10864,22 @@
         <v>10</v>
       </c>
       <c r="C197" s="79" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D197" s="83" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E197" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F197" s="75" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G197" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H197" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I197" s="74" t="s">
         <v>12</v>
@@ -10809,22 +10896,22 @@
         <v>10</v>
       </c>
       <c r="C198" s="75" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D198" s="77" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E198" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F198" s="75" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="G198" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H198" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I198" s="74" t="s">
         <v>12</v>
@@ -10841,22 +10928,22 @@
         <v>10</v>
       </c>
       <c r="C199" s="75" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D199" s="83" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E199" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F199" s="75" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="G199" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H199" s="74" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I199" s="74" t="s">
         <v>12</v>
@@ -10866,18 +10953,18 @@
       </c>
     </row>
     <row r="200" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="104" t="s">
-        <v>602</v>
-      </c>
-      <c r="B200" s="104"/>
-      <c r="C200" s="104"/>
-      <c r="D200" s="104"/>
-      <c r="E200" s="104"/>
-      <c r="F200" s="104"/>
-      <c r="G200" s="104"/>
-      <c r="H200" s="104"/>
-      <c r="I200" s="104"/>
-      <c r="J200" s="104"/>
+      <c r="A200" s="103" t="s">
+        <v>599</v>
+      </c>
+      <c r="B200" s="103"/>
+      <c r="C200" s="103"/>
+      <c r="D200" s="103"/>
+      <c r="E200" s="103"/>
+      <c r="F200" s="103"/>
+      <c r="G200" s="103"/>
+      <c r="H200" s="103"/>
+      <c r="I200" s="103"/>
+      <c r="J200" s="103"/>
     </row>
     <row r="201" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="73">
@@ -10887,22 +10974,22 @@
         <v>10</v>
       </c>
       <c r="C201" s="75" t="s">
+        <v>631</v>
+      </c>
+      <c r="D201" s="77" t="s">
         <v>634</v>
-      </c>
-      <c r="D201" s="77" t="s">
-        <v>637</v>
       </c>
       <c r="E201" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F201" s="75" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="G201" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H201" s="74" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I201" s="74" t="s">
         <v>12</v>
@@ -10912,18 +10999,18 @@
       </c>
     </row>
     <row r="202" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="96" t="s">
-        <v>665</v>
-      </c>
-      <c r="B202" s="96"/>
-      <c r="C202" s="96"/>
-      <c r="D202" s="96"/>
-      <c r="E202" s="96"/>
-      <c r="F202" s="96"/>
-      <c r="G202" s="96"/>
-      <c r="H202" s="96"/>
-      <c r="I202" s="96"/>
-      <c r="J202" s="96"/>
+      <c r="A202" s="101" t="s">
+        <v>662</v>
+      </c>
+      <c r="B202" s="101"/>
+      <c r="C202" s="101"/>
+      <c r="D202" s="101"/>
+      <c r="E202" s="101"/>
+      <c r="F202" s="101"/>
+      <c r="G202" s="101"/>
+      <c r="H202" s="101"/>
+      <c r="I202" s="101"/>
+      <c r="J202" s="101"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="88">
@@ -10933,22 +11020,22 @@
         <v>10</v>
       </c>
       <c r="C203" s="89" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D203" s="45" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E203" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F203" s="89" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="G203" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H203" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I203" s="51" t="s">
         <v>12</v>
@@ -10965,22 +11052,22 @@
         <v>10</v>
       </c>
       <c r="C204" s="87" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E204" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F204" s="87" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G204" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H204" s="48" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I204" s="48" t="s">
         <v>12</v>
@@ -10997,22 +11084,22 @@
         <v>10</v>
       </c>
       <c r="C205" s="87" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E205" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F205" s="87" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G205" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H205" s="48" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I205" s="48" t="s">
         <v>12</v>
@@ -11029,22 +11116,22 @@
         <v>10</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D206" s="28" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E206" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F206" s="28" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G206" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H206" s="28" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I206" s="28" t="s">
         <v>12</v>
@@ -11061,22 +11148,22 @@
         <v>10</v>
       </c>
       <c r="C207" s="28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D207" s="28" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E207" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F207" s="28" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G207" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H207" s="28" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I207" s="28" t="s">
         <v>12</v>
@@ -11093,22 +11180,22 @@
         <v>10</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D208" s="28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E208" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F208" s="28" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G208" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H208" s="28" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I208" s="28" t="s">
         <v>12</v>
@@ -11125,22 +11212,22 @@
         <v>10</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D209" s="28" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E209" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F209" s="28" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="G209" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H209" s="28" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I209" s="28" t="s">
         <v>12</v>
@@ -11150,18 +11237,18 @@
       </c>
     </row>
     <row r="210" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="96" t="s">
-        <v>731</v>
-      </c>
-      <c r="B210" s="96"/>
-      <c r="C210" s="96"/>
-      <c r="D210" s="96"/>
-      <c r="E210" s="96"/>
-      <c r="F210" s="96"/>
-      <c r="G210" s="96"/>
-      <c r="H210" s="96"/>
-      <c r="I210" s="96"/>
-      <c r="J210" s="96"/>
+      <c r="A210" s="101" t="s">
+        <v>728</v>
+      </c>
+      <c r="B210" s="101"/>
+      <c r="C210" s="101"/>
+      <c r="D210" s="101"/>
+      <c r="E210" s="101"/>
+      <c r="F210" s="101"/>
+      <c r="G210" s="101"/>
+      <c r="H210" s="101"/>
+      <c r="I210" s="101"/>
+      <c r="J210" s="101"/>
     </row>
     <row r="211" spans="1:10" s="92" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="91">
@@ -11171,22 +11258,22 @@
         <v>10</v>
       </c>
       <c r="C211" s="89" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D211" s="94" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E211" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="89" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="G211" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H211" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I211" s="51" t="s">
         <v>12</v>
@@ -11203,22 +11290,22 @@
         <v>10</v>
       </c>
       <c r="C212" s="89" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D212" s="45" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E212" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F212" s="89" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G212" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H212" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I212" s="51" t="s">
         <v>12</v>
@@ -11235,22 +11322,22 @@
         <v>10</v>
       </c>
       <c r="C213" s="89" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D213" s="45" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E213" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F213" s="89" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="G213" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H213" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I213" s="51" t="s">
         <v>12</v>
@@ -11267,22 +11354,22 @@
         <v>10</v>
       </c>
       <c r="C214" s="89" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D214" s="45" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E214" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F214" s="89" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G214" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H214" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I214" s="51" t="s">
         <v>12</v>
@@ -11299,22 +11386,22 @@
         <v>10</v>
       </c>
       <c r="C215" s="89" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D215" s="45" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E215" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F215" s="89" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G215" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H215" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I215" s="51" t="s">
         <v>12</v>
@@ -11331,22 +11418,22 @@
         <v>10</v>
       </c>
       <c r="C216" s="89" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D216" s="45" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E216" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F216" s="89" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G216" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I216" s="51" t="s">
         <v>12</v>
@@ -11363,22 +11450,22 @@
         <v>10</v>
       </c>
       <c r="C217" s="89" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D217" s="45" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E217" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F217" s="89" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G217" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H217" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I217" s="51" t="s">
         <v>12</v>
@@ -11395,22 +11482,22 @@
         <v>10</v>
       </c>
       <c r="C218" s="89" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D218" s="45" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E218" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F218" s="89" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="G218" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H218" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I218" s="51" t="s">
         <v>12</v>
@@ -11427,22 +11514,22 @@
         <v>10</v>
       </c>
       <c r="C219" s="89" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D219" s="45" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E219" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F219" s="89" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G219" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H219" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I219" s="51" t="s">
         <v>12</v>
@@ -11459,22 +11546,22 @@
         <v>10</v>
       </c>
       <c r="C220" s="89" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D220" s="45" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E220" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F220" s="89" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="G220" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H220" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I220" s="51" t="s">
         <v>12</v>
@@ -11491,22 +11578,22 @@
         <v>10</v>
       </c>
       <c r="C221" s="89" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D221" s="45" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E221" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F221" s="89" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G221" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H221" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I221" s="51" t="s">
         <v>12</v>
@@ -11523,22 +11610,22 @@
         <v>10</v>
       </c>
       <c r="C222" s="89" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D222" s="45" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E222" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F222" s="89" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="G222" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H222" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I222" s="51" t="s">
         <v>12</v>
@@ -11555,22 +11642,22 @@
         <v>10</v>
       </c>
       <c r="C223" s="89" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D223" s="45" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E223" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F223" s="89" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G223" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H223" s="51" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I223" s="51" t="s">
         <v>12</v>
@@ -11580,20 +11667,20 @@
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A224" s="96" t="s">
-        <v>770</v>
-      </c>
-      <c r="B224" s="96"/>
-      <c r="C224" s="96"/>
-      <c r="D224" s="96"/>
-      <c r="E224" s="96"/>
-      <c r="F224" s="96"/>
-      <c r="G224" s="96"/>
-      <c r="H224" s="96"/>
-      <c r="I224" s="96"/>
-      <c r="J224" s="96"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="101" t="s">
+        <v>767</v>
+      </c>
+      <c r="B224" s="101"/>
+      <c r="C224" s="101"/>
+      <c r="D224" s="101"/>
+      <c r="E224" s="101"/>
+      <c r="F224" s="101"/>
+      <c r="G224" s="101"/>
+      <c r="H224" s="101"/>
+      <c r="I224" s="101"/>
+      <c r="J224" s="101"/>
+    </row>
+    <row r="225" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="28">
         <v>1</v>
       </c>
@@ -11601,22 +11688,22 @@
         <v>10</v>
       </c>
       <c r="C225" s="87" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D225" s="95" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E225" s="86" t="s">
         <v>14</v>
       </c>
       <c r="F225" s="87" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="G225" s="86" t="s">
         <v>11</v>
       </c>
       <c r="H225" s="86" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I225" s="86" t="s">
         <v>12</v>
@@ -11625,16 +11712,278 @@
         <v>13</v>
       </c>
     </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="101" t="s">
+        <v>772</v>
+      </c>
+      <c r="B226" s="101"/>
+      <c r="C226" s="101"/>
+      <c r="D226" s="101"/>
+      <c r="E226" s="101"/>
+      <c r="F226" s="101"/>
+      <c r="G226" s="101"/>
+      <c r="H226" s="101"/>
+      <c r="I226" s="101"/>
+      <c r="J226" s="101"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="96">
+        <v>1</v>
+      </c>
+      <c r="B227" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C227" s="87" t="s">
+        <v>774</v>
+      </c>
+      <c r="D227" s="99" t="s">
+        <v>773</v>
+      </c>
+      <c r="E227" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F227" s="98" t="s">
+        <v>775</v>
+      </c>
+      <c r="G227" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I227" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J227" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="96">
+        <v>2</v>
+      </c>
+      <c r="B228" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228" s="87" t="s">
+        <v>777</v>
+      </c>
+      <c r="D228" s="99" t="s">
+        <v>778</v>
+      </c>
+      <c r="E228" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F228" s="98" t="s">
+        <v>776</v>
+      </c>
+      <c r="G228" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I228" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J228" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="95">
+        <v>3</v>
+      </c>
+      <c r="B229" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C229" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="D229" s="95" t="s">
+        <v>779</v>
+      </c>
+      <c r="E229" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F229" s="98" t="s">
+        <v>781</v>
+      </c>
+      <c r="G229" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I229" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J229" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="95">
+        <v>4</v>
+      </c>
+      <c r="B230" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C230" s="87" t="s">
+        <v>782</v>
+      </c>
+      <c r="D230" s="95" t="s">
+        <v>783</v>
+      </c>
+      <c r="E230" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230" s="98" t="s">
+        <v>784</v>
+      </c>
+      <c r="G230" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I230" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J230" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="95">
+        <v>5</v>
+      </c>
+      <c r="B231" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231" s="87" t="s">
+        <v>785</v>
+      </c>
+      <c r="D231" s="95" t="s">
+        <v>786</v>
+      </c>
+      <c r="E231" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F231" s="98" t="s">
+        <v>787</v>
+      </c>
+      <c r="G231" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I231" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J231" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="95">
+        <v>6</v>
+      </c>
+      <c r="B232" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" s="87" t="s">
+        <v>789</v>
+      </c>
+      <c r="D232" s="95" t="s">
+        <v>788</v>
+      </c>
+      <c r="E232" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F232" s="87" t="s">
+        <v>790</v>
+      </c>
+      <c r="G232" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="I232" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J232" s="97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="101" t="s">
+        <v>793</v>
+      </c>
+      <c r="B233" s="101"/>
+      <c r="C233" s="101"/>
+      <c r="D233" s="101"/>
+      <c r="E233" s="101"/>
+      <c r="F233" s="101"/>
+      <c r="G233" s="101"/>
+      <c r="H233" s="101"/>
+      <c r="I233" s="101"/>
+      <c r="J233" s="101"/>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="95">
+        <v>1</v>
+      </c>
+      <c r="B234" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C234" s="87" t="s">
+        <v>796</v>
+      </c>
+      <c r="D234" s="114" t="s">
+        <v>794</v>
+      </c>
+      <c r="E234" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F234" s="87" t="s">
+        <v>795</v>
+      </c>
+      <c r="G234" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="86" t="s">
+        <v>633</v>
+      </c>
+      <c r="I234" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J234" s="86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="96"/>
+      <c r="B235" s="96"/>
+      <c r="C235" s="96"/>
+      <c r="D235" s="96"/>
+      <c r="E235" s="96"/>
+      <c r="F235" s="96"/>
+      <c r="G235" s="96"/>
+      <c r="H235" s="96"/>
+      <c r="I235" s="96"/>
+      <c r="J235" s="96"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A224:J224"/>
+  <mergeCells count="20">
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A59:J59"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A233:J233"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A200:J200"/>
     <mergeCell ref="A192:J192"/>
@@ -11642,9 +11991,13 @@
     <mergeCell ref="A170:J170"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A210:J210"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A224:J224"/>
+    <mergeCell ref="A210:J210"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -11742,7 +12095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X217"/>
+  <dimension ref="A1:X224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -11827,16 +12180,16 @@
         <v>335</v>
       </c>
       <c r="U1" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="W1" s="31" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="X1" s="31" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -12897,7 +13250,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>22</v>
@@ -13247,7 +13600,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>95</v>
@@ -15371,7 +15724,7 @@
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B52" s="48" t="s">
         <v>22</v>
@@ -15443,7 +15796,7 @@
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="47" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B53" s="48" t="s">
         <v>22</v>
@@ -15515,7 +15868,7 @@
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B54" s="48" t="s">
         <v>22</v>
@@ -15587,7 +15940,7 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B55" s="48" t="s">
         <v>22</v>
@@ -15659,7 +16012,7 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B56" s="48" t="s">
         <v>22</v>
@@ -15731,7 +16084,7 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="47" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B57" s="48" t="s">
         <v>22</v>
@@ -17317,7 +17670,7 @@
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="51" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B79" s="51" t="s">
         <v>22</v>
@@ -17391,7 +17744,7 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="51" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B80" s="51" t="s">
         <v>22</v>
@@ -19389,7 +19742,7 @@
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="48" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B107" s="51" t="s">
         <v>22</v>
@@ -20129,7 +20482,7 @@
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="48" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B117" s="48" t="s">
         <v>22</v>
@@ -20949,7 +21302,7 @@
         <v>22</v>
       </c>
       <c r="C128" s="36" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D128" s="48" t="s">
         <v>22</v>
@@ -20958,22 +21311,22 @@
         <v>22</v>
       </c>
       <c r="F128" s="48" t="s">
+        <v>477</v>
+      </c>
+      <c r="G128" s="100" t="s">
+        <v>791</v>
+      </c>
+      <c r="H128" s="48" t="s">
         <v>478</v>
       </c>
-      <c r="G128" s="49" t="s">
+      <c r="I128" s="48" t="s">
         <v>479</v>
       </c>
-      <c r="H128" s="48" t="s">
+      <c r="J128" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="K128" s="48" t="s">
         <v>480</v>
-      </c>
-      <c r="I128" s="48" t="s">
-        <v>481</v>
-      </c>
-      <c r="J128" s="36" t="s">
-        <v>461</v>
-      </c>
-      <c r="K128" s="48" t="s">
-        <v>482</v>
       </c>
       <c r="L128" s="48" t="s">
         <v>22</v>
@@ -21097,32 +21450,32 @@
         <v>22</v>
       </c>
       <c r="C130" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="D130" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="48" t="s">
         <v>457</v>
       </c>
-      <c r="D130" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E130" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F130" s="48" t="s">
+      <c r="G130" s="49" t="s">
         <v>458</v>
-      </c>
-      <c r="G130" s="49" t="s">
-        <v>459</v>
       </c>
       <c r="H130" s="48" t="s">
         <v>37</v>
       </c>
       <c r="I130" s="48" t="s">
+        <v>459</v>
+      </c>
+      <c r="J130" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="J130" s="36" t="s">
+      <c r="K130" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="K130" s="48" t="s">
-        <v>462</v>
-      </c>
       <c r="L130" s="48" t="s">
         <v>22</v>
       </c>
@@ -21163,7 +21516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="48" t="s">
         <v>407</v>
       </c>
@@ -21171,7 +21524,7 @@
         <v>22</v>
       </c>
       <c r="C131" s="36" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D131" s="48" t="s">
         <v>22</v>
@@ -21180,23 +21533,23 @@
         <v>22</v>
       </c>
       <c r="F131" s="48" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G131" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="H131" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="H131" s="48" t="s">
-        <v>466</v>
-      </c>
       <c r="I131" s="48" t="s">
+        <v>481</v>
+      </c>
+      <c r="J131" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="K131" s="48" t="s">
         <v>483</v>
       </c>
-      <c r="J131" s="36" t="s">
-        <v>484</v>
-      </c>
-      <c r="K131" s="48" t="s">
-        <v>485</v>
-      </c>
       <c r="L131" s="48" t="s">
         <v>22</v>
       </c>
@@ -21237,7 +21590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="48" t="s">
         <v>409</v>
       </c>
@@ -21245,7 +21598,7 @@
         <v>22</v>
       </c>
       <c r="C132" s="36" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D132" s="48" t="s">
         <v>22</v>
@@ -21257,20 +21610,20 @@
         <v>29</v>
       </c>
       <c r="G132" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="H132" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="H132" s="48" t="s">
+      <c r="I132" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="I132" s="48" t="s">
+      <c r="J132" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="J132" s="36" t="s">
+      <c r="K132" s="48" t="s">
         <v>468</v>
       </c>
-      <c r="K132" s="48" t="s">
-        <v>469</v>
-      </c>
       <c r="L132" s="48" t="s">
         <v>22</v>
       </c>
@@ -21311,7 +21664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="48" t="s">
         <v>412</v>
       </c>
@@ -21319,7 +21672,7 @@
         <v>22</v>
       </c>
       <c r="C133" s="36" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D133" s="48" t="s">
         <v>22</v>
@@ -21328,22 +21681,22 @@
         <v>22</v>
       </c>
       <c r="F133" s="48" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G133" s="49" t="s">
-        <v>488</v>
+        <v>791</v>
       </c>
       <c r="H133" s="48" t="s">
         <v>38</v>
       </c>
       <c r="I133" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J133" s="36" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="K133" s="48" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L133" s="48" t="s">
         <v>22</v>
@@ -21533,7 +21886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="48" t="s">
         <v>421</v>
       </c>
@@ -21541,7 +21894,7 @@
         <v>22</v>
       </c>
       <c r="C136" s="36" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D136" s="48" t="s">
         <v>22</v>
@@ -21553,19 +21906,19 @@
         <v>29</v>
       </c>
       <c r="G136" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="H136" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="H136" s="48" t="s">
+      <c r="I136" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="I136" s="48" t="s">
-        <v>467</v>
-      </c>
       <c r="J136" s="36" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="K136" s="48" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L136" s="48" t="s">
         <v>22</v>
@@ -21609,7 +21962,7 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B137" s="48" t="s">
         <v>22</v>
@@ -21891,13 +22244,13 @@
         <v>22</v>
       </c>
       <c r="U140" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="V140" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="W140" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="X140" s="48" t="s">
         <v>22</v>
@@ -21965,13 +22318,13 @@
         <v>22</v>
       </c>
       <c r="U141" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="V141" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W141" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="X141" s="48" t="s">
         <v>22</v>
@@ -22039,13 +22392,13 @@
         <v>22</v>
       </c>
       <c r="U142" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="V142" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="W142" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="X142" s="48" t="s">
         <v>22</v>
@@ -22113,13 +22466,13 @@
         <v>22</v>
       </c>
       <c r="U143" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="V143" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="W143" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="X143" s="48" t="s">
         <v>22</v>
@@ -22187,13 +22540,13 @@
         <v>22</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W144" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X144" s="48" t="s">
         <v>22</v>
@@ -22261,13 +22614,13 @@
         <v>22</v>
       </c>
       <c r="U145" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V145" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W145" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X145" s="48" t="s">
         <v>22</v>
@@ -22275,7 +22628,7 @@
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="48" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B146" s="48" t="s">
         <v>22</v>
@@ -22335,13 +22688,13 @@
         <v>22</v>
       </c>
       <c r="U146" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V146" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W146" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X146" s="48" t="s">
         <v>22</v>
@@ -22349,7 +22702,7 @@
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" s="48" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B147" s="48" t="s">
         <v>22</v>
@@ -22409,13 +22762,13 @@
         <v>22</v>
       </c>
       <c r="U147" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V147" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W147" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X147" s="48" t="s">
         <v>22</v>
@@ -22423,7 +22776,7 @@
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="48" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B148" s="48" t="s">
         <v>22</v>
@@ -22483,13 +22836,13 @@
         <v>22</v>
       </c>
       <c r="U148" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V148" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W148" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X148" s="48" t="s">
         <v>22</v>
@@ -22497,7 +22850,7 @@
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" s="48" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B149" s="48" t="s">
         <v>22</v>
@@ -22557,13 +22910,13 @@
         <v>22</v>
       </c>
       <c r="U149" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V149" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W149" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X149" s="48" t="s">
         <v>22</v>
@@ -22571,7 +22924,7 @@
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B150" s="48" t="s">
         <v>22</v>
@@ -22631,13 +22984,13 @@
         <v>22</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W150" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X150" s="48" t="s">
         <v>22</v>
@@ -22645,7 +22998,7 @@
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="48" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B151" s="48" t="s">
         <v>22</v>
@@ -22705,13 +23058,13 @@
         <v>22</v>
       </c>
       <c r="U151" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V151" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W151" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X151" s="48" t="s">
         <v>22</v>
@@ -22719,7 +23072,7 @@
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" s="48" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B152" s="48" t="s">
         <v>22</v>
@@ -22779,13 +23132,13 @@
         <v>22</v>
       </c>
       <c r="U152" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V152" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W152" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X152" s="48" t="s">
         <v>22</v>
@@ -22793,7 +23146,7 @@
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" s="48" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B153" s="48" t="s">
         <v>22</v>
@@ -22853,13 +23206,13 @@
         <v>22</v>
       </c>
       <c r="U153" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V153" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W153" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X153" s="48" t="s">
         <v>22</v>
@@ -22867,7 +23220,7 @@
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" s="48" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B154" s="48" t="s">
         <v>22</v>
@@ -22927,13 +23280,13 @@
         <v>22</v>
       </c>
       <c r="U154" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V154" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W154" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X154" s="48" t="s">
         <v>22</v>
@@ -22941,7 +23294,7 @@
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" s="48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B155" s="48" t="s">
         <v>22</v>
@@ -23015,7 +23368,7 @@
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B156" s="48" t="s">
         <v>22</v>
@@ -23089,7 +23442,7 @@
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" s="48" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B157" s="48" t="s">
         <v>22</v>
@@ -23163,7 +23516,7 @@
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B158" s="48" t="s">
         <v>22</v>
@@ -23223,13 +23576,13 @@
         <v>22</v>
       </c>
       <c r="U158" s="48" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="V158" s="48" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="W158" s="48" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="X158" s="48" t="s">
         <v>22</v>
@@ -23237,7 +23590,7 @@
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" s="48" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B159" s="48" t="s">
         <v>22</v>
@@ -23297,13 +23650,13 @@
         <v>22</v>
       </c>
       <c r="U159" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="V159" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W159" s="48" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="X159" s="48" t="s">
         <v>22</v>
@@ -23311,7 +23664,7 @@
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="48" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B160" s="48" t="s">
         <v>22</v>
@@ -23371,13 +23724,13 @@
         <v>22</v>
       </c>
       <c r="U160" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="V160" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="W160" s="48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="X160" s="48" t="s">
         <v>22</v>
@@ -23385,7 +23738,7 @@
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" s="48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B161" s="48" t="s">
         <v>22</v>
@@ -23445,13 +23798,13 @@
         <v>22</v>
       </c>
       <c r="U161" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="V161" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="W161" s="48" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="X161" s="48" t="s">
         <v>22</v>
@@ -23459,7 +23812,7 @@
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B162" s="48" t="s">
         <v>22</v>
@@ -23519,13 +23872,13 @@
         <v>22</v>
       </c>
       <c r="U162" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V162" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W162" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X162" s="48" t="s">
         <v>22</v>
@@ -23533,7 +23886,7 @@
     </row>
     <row r="163" spans="1:24" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A163" s="48" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B163" s="48" t="s">
         <v>22</v>
@@ -23593,13 +23946,13 @@
         <v>22</v>
       </c>
       <c r="U163" s="48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="V163" s="48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="W163" s="48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="X163" s="48" t="s">
         <v>22</v>
@@ -23607,7 +23960,7 @@
     </row>
     <row r="164" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A164" s="48" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B164" s="48" t="s">
         <v>22</v>
@@ -23667,13 +24020,13 @@
         <v>22</v>
       </c>
       <c r="U164" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="V164" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="W164" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X164" s="48" t="s">
         <v>22</v>
@@ -23681,7 +24034,7 @@
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" s="48" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B165" s="48" t="s">
         <v>22</v>
@@ -23755,7 +24108,7 @@
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" s="48" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B166" s="48" t="s">
         <v>22</v>
@@ -23829,7 +24182,7 @@
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" s="48" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B167" s="48" t="s">
         <v>22</v>
@@ -23903,7 +24256,7 @@
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="48" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B168" s="48" t="s">
         <v>22</v>
@@ -23977,7 +24330,7 @@
     </row>
     <row r="169" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="48" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B169" s="48" t="s">
         <v>22</v>
@@ -24051,7 +24404,7 @@
     </row>
     <row r="170" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="67" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B170" s="48" t="s">
         <v>22</v>
@@ -24125,7 +24478,7 @@
     </row>
     <row r="171" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="70" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B171" s="48" t="s">
         <v>22</v>
@@ -24199,7 +24552,7 @@
     </row>
     <row r="172" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="67" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B172" s="48" t="s">
         <v>22</v>
@@ -24273,7 +24626,7 @@
     </row>
     <row r="173" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="70" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -24347,7 +24700,7 @@
     </row>
     <row r="174" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="67" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B174" s="48" t="s">
         <v>22</v>
@@ -24421,7 +24774,7 @@
     </row>
     <row r="175" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="70" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B175" s="48" t="s">
         <v>22</v>
@@ -24495,7 +24848,7 @@
     </row>
     <row r="176" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="67" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B176" s="48" t="s">
         <v>22</v>
@@ -24569,7 +24922,7 @@
     </row>
     <row r="177" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="70" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B177" s="48" t="s">
         <v>22</v>
@@ -24643,7 +24996,7 @@
     </row>
     <row r="178" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="67" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B178" s="48" t="s">
         <v>22</v>
@@ -24717,7 +25070,7 @@
     </row>
     <row r="179" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="70" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B179" s="48" t="s">
         <v>22</v>
@@ -24791,7 +25144,7 @@
     </row>
     <row r="180" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="67" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B180" s="48" t="s">
         <v>22</v>
@@ -24865,7 +25218,7 @@
     </row>
     <row r="181" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="70" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B181" s="48" t="s">
         <v>22</v>
@@ -24939,7 +25292,7 @@
     </row>
     <row r="182" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="67" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B182" s="48" t="s">
         <v>22</v>
@@ -25013,7 +25366,7 @@
     </row>
     <row r="183" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="70" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B183" s="48" t="s">
         <v>22</v>
@@ -25087,7 +25440,7 @@
     </row>
     <row r="184" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="67" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B184" s="48" t="s">
         <v>22</v>
@@ -25161,7 +25514,7 @@
     </row>
     <row r="185" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="67" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B185" s="48" t="s">
         <v>22</v>
@@ -25235,7 +25588,7 @@
     </row>
     <row r="186" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="67" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B186" s="48" t="s">
         <v>22</v>
@@ -25309,37 +25662,37 @@
     </row>
     <row r="187" spans="1:24" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="67" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B187" s="48" t="s">
         <v>64</v>
       </c>
       <c r="C187" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="D187" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E187" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F187" s="48" t="s">
         <v>463</v>
       </c>
-      <c r="D187" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E187" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F187" s="48" t="s">
+      <c r="G187" s="49" t="s">
         <v>464</v>
       </c>
-      <c r="G187" s="49" t="s">
+      <c r="H187" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="H187" s="48" t="s">
-        <v>466</v>
-      </c>
       <c r="I187" s="48" t="s">
+        <v>481</v>
+      </c>
+      <c r="J187" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="K187" s="48" t="s">
         <v>483</v>
-      </c>
-      <c r="J187" s="36" t="s">
-        <v>484</v>
-      </c>
-      <c r="K187" s="48" t="s">
-        <v>485</v>
       </c>
       <c r="L187" s="48" t="s">
         <v>22</v>
@@ -25409,7 +25762,7 @@
     </row>
     <row r="189" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="75" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B189" s="48" t="s">
         <v>22</v>
@@ -25463,7 +25816,7 @@
         <v>22</v>
       </c>
       <c r="S189" s="49" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T189" s="48" t="s">
         <v>22</v>
@@ -25472,10 +25825,10 @@
         <v>22</v>
       </c>
       <c r="V189" s="48" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="W189" s="36" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="X189" s="48" t="s">
         <v>22</v>
@@ -25483,7 +25836,7 @@
     </row>
     <row r="190" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="75" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B190" s="48" t="s">
         <v>22</v>
@@ -25537,7 +25890,7 @@
         <v>22</v>
       </c>
       <c r="S190" s="49" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T190" s="48" t="s">
         <v>22</v>
@@ -25552,12 +25905,12 @@
         <v>22</v>
       </c>
       <c r="X190" s="78" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="191" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="75" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B191" s="48" t="s">
         <v>22</v>
@@ -25611,7 +25964,7 @@
         <v>22</v>
       </c>
       <c r="S191" s="49" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T191" s="48" t="s">
         <v>22</v>
@@ -25626,12 +25979,12 @@
         <v>22</v>
       </c>
       <c r="X191" s="84" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="192" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="75" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B192" s="48" t="s">
         <v>22</v>
@@ -25685,7 +26038,7 @@
         <v>22</v>
       </c>
       <c r="S192" s="49" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T192" s="48" t="s">
         <v>22</v>
@@ -25694,7 +26047,7 @@
         <v>22</v>
       </c>
       <c r="V192" s="48" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="W192" s="36" t="s">
         <v>22</v>
@@ -25705,7 +26058,7 @@
     </row>
     <row r="193" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="75" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B193" s="48" t="s">
         <v>22</v>
@@ -25759,7 +26112,7 @@
         <v>22</v>
       </c>
       <c r="S193" s="49" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T193" s="48" t="s">
         <v>22</v>
@@ -25779,7 +26132,7 @@
     </row>
     <row r="194" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="75" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B194" s="48" t="s">
         <v>22</v>
@@ -25833,7 +26186,7 @@
         <v>22</v>
       </c>
       <c r="S194" s="49" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T194" s="48" t="s">
         <v>22</v>
@@ -25848,12 +26201,12 @@
         <v>22</v>
       </c>
       <c r="X194" s="85" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="75" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B195" s="48" t="s">
         <v>22</v>
@@ -25907,7 +26260,7 @@
         <v>22</v>
       </c>
       <c r="S195" s="49" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="T195" s="48" t="s">
         <v>22</v>
@@ -25927,7 +26280,7 @@
     </row>
     <row r="196" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="75" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B196" s="48" t="s">
         <v>22</v>
@@ -26001,7 +26354,7 @@
     </row>
     <row r="197" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="75" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B197" s="48" t="s">
         <v>22</v>
@@ -26075,7 +26428,7 @@
     </row>
     <row r="198" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="75" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B198" s="48" t="s">
         <v>22</v>
@@ -26149,7 +26502,7 @@
     </row>
     <row r="199" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="75" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B199" s="48" t="s">
         <v>22</v>
@@ -26223,7 +26576,7 @@
     </row>
     <row r="200" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="75" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B200" s="48" t="s">
         <v>22</v>
@@ -26297,7 +26650,7 @@
     </row>
     <row r="201" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="75" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B201" s="48" t="s">
         <v>22</v>
@@ -26371,7 +26724,7 @@
     </row>
     <row r="202" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="75" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B202" s="48" t="s">
         <v>22</v>
@@ -26445,7 +26798,7 @@
     </row>
     <row r="203" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="75" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B203" s="48" t="s">
         <v>22</v>
@@ -26519,7 +26872,7 @@
     </row>
     <row r="204" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A204" s="89" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B204" s="48" t="s">
         <v>22</v>
@@ -26593,7 +26946,7 @@
     </row>
     <row r="205" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A205" s="89" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B205" s="48" t="s">
         <v>22</v>
@@ -26667,7 +27020,7 @@
     </row>
     <row r="206" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A206" s="89" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B206" s="48" t="s">
         <v>22</v>
@@ -26741,7 +27094,7 @@
     </row>
     <row r="207" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A207" s="89" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B207" s="48" t="s">
         <v>22</v>
@@ -26815,7 +27168,7 @@
     </row>
     <row r="208" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A208" s="89" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B208" s="48" t="s">
         <v>22</v>
@@ -26889,7 +27242,7 @@
     </row>
     <row r="209" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A209" s="89" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B209" s="48" t="s">
         <v>22</v>
@@ -26963,7 +27316,7 @@
     </row>
     <row r="210" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A210" s="89" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B210" s="48" t="s">
         <v>22</v>
@@ -27037,7 +27390,7 @@
     </row>
     <row r="211" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A211" s="89" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B211" s="48" t="s">
         <v>22</v>
@@ -27111,7 +27464,7 @@
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212" s="89" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B212" s="48" t="s">
         <v>22</v>
@@ -27185,7 +27538,7 @@
     </row>
     <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213" s="89" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B213" s="48" t="s">
         <v>22</v>
@@ -27259,7 +27612,7 @@
     </row>
     <row r="214" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A214" s="89" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B214" s="48" t="s">
         <v>22</v>
@@ -27333,7 +27686,7 @@
     </row>
     <row r="215" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A215" s="89" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B215" s="48" t="s">
         <v>22</v>
@@ -27407,7 +27760,7 @@
     </row>
     <row r="216" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A216" s="87" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B216" s="48" t="s">
         <v>22</v>
@@ -27481,7 +27834,7 @@
     </row>
     <row r="217" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A217" s="87" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B217" s="48" t="s">
         <v>22</v>
@@ -27550,6 +27903,524 @@
         <v>22</v>
       </c>
       <c r="X217" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A218" s="87" t="s">
+        <v>775</v>
+      </c>
+      <c r="B218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V218" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W218" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X218" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A219" s="87" t="s">
+        <v>776</v>
+      </c>
+      <c r="B219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V219" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W219" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X219" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A220" s="87" t="s">
+        <v>781</v>
+      </c>
+      <c r="B220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V220" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W220" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X220" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A221" s="87" t="s">
+        <v>784</v>
+      </c>
+      <c r="B221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V221" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W221" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X221" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A222" s="87" t="s">
+        <v>787</v>
+      </c>
+      <c r="B222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V222" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W222" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X222" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A223" s="87" t="s">
+        <v>790</v>
+      </c>
+      <c r="B223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V223" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W223" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X223" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A224" s="87" t="s">
+        <v>795</v>
+      </c>
+      <c r="B224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V224" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W224" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X224" s="48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -27673,16 +28544,16 @@
     <hyperlink ref="G132" r:id="rId11" xr:uid="{21D57B30-A62F-4B04-8FC4-754A1492DE18}"/>
     <hyperlink ref="G136" r:id="rId12" xr:uid="{757DF638-4C34-42A1-BA8F-AD4541A38734}"/>
     <hyperlink ref="G131" r:id="rId13" xr:uid="{98E0996F-0FB4-4189-BE73-57E37E31FC3F}"/>
-    <hyperlink ref="G128" r:id="rId14" xr:uid="{009DD950-489A-4511-9EE8-3302596C4B91}"/>
-    <hyperlink ref="G133" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
-    <hyperlink ref="D143" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
-    <hyperlink ref="G187" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
-    <hyperlink ref="S189" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
-    <hyperlink ref="S191" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
-    <hyperlink ref="S192" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
-    <hyperlink ref="S193" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
-    <hyperlink ref="X190" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
-    <hyperlink ref="X194" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
+    <hyperlink ref="D143" r:id="rId14" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
+    <hyperlink ref="G187" r:id="rId15" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
+    <hyperlink ref="S189" r:id="rId16" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S191" r:id="rId17" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S192" r:id="rId18" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="S193" r:id="rId19" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
+    <hyperlink ref="X190" r:id="rId20" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X194" r:id="rId21" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
+    <hyperlink ref="G128" r:id="rId22" xr:uid="{180E7A34-8CAF-4D13-A6B9-90BAFFBE176C}"/>
+    <hyperlink ref="G133" r:id="rId23" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>
